--- a/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_2_child.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_2_child.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\octobre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5CEF92-9D70-426A-813A-0E22DFEC4283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE4656A-D5FA-4029-ABAD-F6491644CB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="261">
   <si>
     <t>type</t>
   </si>
@@ -708,18 +708,12 @@
     <t>bind::db_filter_by_col_4</t>
   </si>
   <si>
-    <t>if(${p_region}='DIOURBEL' or ${p_region}='LOUGA (PRATIQUE)' or ${p_region}='MATAM', . &gt;= 10 and . &lt;= 14, . &gt;= 5 and . &lt;= 14)</t>
-  </si>
-  <si>
     <t>L’âge doit être compris entre 5 et 14 ans pour l'enquête complémentaire, entre 10 et 14 ans pour l'enquête d'évaluation pratique</t>
   </si>
   <si>
     <t>p_sppa2510</t>
   </si>
   <si>
-    <t>(2025 Oct) - 2. SCH/STH – Participant</t>
-  </si>
-  <si>
     <t>C1</t>
   </si>
   <si>
@@ -741,12 +735,6 @@
     <t>This code has already been used!</t>
   </si>
   <si>
-    <t>select_one barcode_method</t>
-  </si>
-  <si>
-    <t>p_barcode_method</t>
-  </si>
-  <si>
     <t>barcode_method</t>
   </si>
   <si>
@@ -762,46 +750,88 @@
     <t>Saisie manuelle (en cas de panne du scanner)</t>
   </si>
   <si>
-    <t>Veuillez ressaisir le code QR / code-barres</t>
-  </si>
-  <si>
-    <t>${p_barcode_method} = 'QRManual'</t>
-  </si>
-  <si>
     <t>p_code_id1</t>
   </si>
   <si>
-    <t>p_code_id2</t>
-  </si>
-  <si>
-    <t>barcode</t>
-  </si>
-  <si>
-    <t>Veuillez saisir le code QR/code-barres</t>
-  </si>
-  <si>
-    <t>Veuillez scanner le code-barres</t>
-  </si>
-  <si>
-    <t>Méthode de capture code QR / code-barres</t>
-  </si>
-  <si>
-    <t>Veuillez répété le code QR/code-barres</t>
-  </si>
-  <si>
-    <t>. = ${p_code_id1}</t>
-  </si>
-  <si>
-    <t>${p_barcode_method} = 'QRScann'</t>
-  </si>
-  <si>
-    <t>if(${p_barcode_method} = 'QRManual', concat(${p_code_id1}), concat(${p_code_id3}))</t>
-  </si>
-  <si>
-    <t>p_code_id3</t>
-  </si>
-  <si>
-    <t>sn_sppa_impact_2510_2_child</t>
+    <t>select_one warning_note</t>
+  </si>
+  <si>
+    <t>p_warning_note1</t>
+  </si>
+  <si>
+    <t>p_index_init</t>
+  </si>
+  <si>
+    <t>once(if(${last-saved#p_index_cur}!=null,${last-saved#p_index_cur}, 0))</t>
+  </si>
+  <si>
+    <t>p_index</t>
+  </si>
+  <si>
+    <t>The order number of this participant is :</t>
+  </si>
+  <si>
+    <t>${p_index_init} + position(..)</t>
+  </si>
+  <si>
+    <t>position</t>
+  </si>
+  <si>
+    <t>p_index_cur</t>
+  </si>
+  <si>
+    <t>${p_index_init} + indexed-repeat(${position}, ${p_sppa2510}, count(${p_sppa2510}))</t>
+  </si>
+  <si>
+    <t>concat(${p_code_id1})</t>
+  </si>
+  <si>
+    <t>Remarque importante pour les enregistreurs : Avec l'option de génération automatique de codes d'identification, un seul téléphone/une seule tablette doit être utilisé pour enregistrer tous les participants de cette communauté/village (site d'enquête). L'utilisation de plusieurs appareils peut entraîner la duplication des codes d'identification, compromettant ainsi l'intégrité des données.</t>
+  </si>
+  <si>
+    <t>warning_note</t>
+  </si>
+  <si>
+    <t>Compris</t>
+  </si>
+  <si>
+    <t>J'ai lu et compris</t>
+  </si>
+  <si>
+    <t>concat(${p_site_code}, '-', ${p_index_init} + position(..))</t>
+  </si>
+  <si>
+    <t>sn_sppa_impact_2510_2_child_v2</t>
+  </si>
+  <si>
+    <t>(2025 Oct) - 2. SCH/STH – Participant V2</t>
+  </si>
+  <si>
+    <t>type_enquete_list</t>
+  </si>
+  <si>
+    <t>COMPLEMENTAIRE</t>
+  </si>
+  <si>
+    <t>PRATIQUE</t>
+  </si>
+  <si>
+    <t>select_one type_enquete_list</t>
+  </si>
+  <si>
+    <t>Type d'enquete:</t>
+  </si>
+  <si>
+    <t>p_type_enquete</t>
+  </si>
+  <si>
+    <t>if(${p_region}='COMPLEMENTAIRE', . &gt;= 5 and . &lt;= 14, . &gt;= 10 and . &lt;= 14)</t>
+  </si>
+  <si>
+    <t>Ne fréquente pas</t>
+  </si>
+  <si>
+    <t>Ne.fréquente.pas</t>
   </si>
 </sst>
 </file>
@@ -894,7 +924,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -939,8 +969,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -1012,7 +1054,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1172,17 +1214,36 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1467,8 +1528,8 @@
     <col min="3" max="3" width="47.5" style="16" customWidth="1"/>
     <col min="4" max="4" width="47.375" customWidth="1"/>
     <col min="5" max="5" width="12.625" customWidth="1"/>
-    <col min="6" max="6" width="16.875" customWidth="1"/>
-    <col min="7" max="7" width="29.5" customWidth="1"/>
+    <col min="6" max="6" width="109.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.75" customWidth="1"/>
     <col min="8" max="8" width="31.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.875" customWidth="1"/>
     <col min="10" max="10" width="9.75" customWidth="1"/>
@@ -1542,7 +1603,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>14</v>
       </c>
@@ -1757,13 +1818,13 @@
       <c r="B8" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="44" t="s">
         <v>181</v>
       </c>
       <c r="D8" s="44"/>
       <c r="E8" s="42"/>
       <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
+      <c r="G8" s="44"/>
       <c r="H8" s="42"/>
       <c r="I8" s="42"/>
       <c r="J8" s="42"/>
@@ -1779,126 +1840,128 @@
       <c r="T8" s="45"/>
       <c r="U8" s="45"/>
     </row>
-    <row r="9" spans="1:21" s="15" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="44"/>
+    <row r="9" spans="1:21" s="28" customFormat="1" ht="126" x14ac:dyDescent="0.25">
+      <c r="A9" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>245</v>
+      </c>
       <c r="D9" s="44"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45"/>
-      <c r="O9" s="45"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="45"/>
-      <c r="U9" s="45"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
+      <c r="S9" s="34"/>
+      <c r="T9" s="34"/>
+      <c r="U9" s="34"/>
     </row>
     <row r="10" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="65" t="s">
         <v>183</v>
       </c>
-      <c r="B10" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="33"/>
-      <c r="N10" s="33" t="s">
+      <c r="B10" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65" t="s">
+        <v>237</v>
+      </c>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="65"/>
+      <c r="M10" s="65"/>
+      <c r="N10" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" s="65"/>
+    </row>
+    <row r="11" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="34"/>
-      <c r="S10" s="34"/>
-      <c r="T10" s="34"/>
-      <c r="U10" s="34"/>
-    </row>
-    <row r="11" spans="1:21" s="29" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="34"/>
+      <c r="T11" s="34"/>
+      <c r="U11" s="34"/>
+    </row>
+    <row r="12" spans="1:21" s="29" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="B11" s="48" t="s">
-        <v>221</v>
-      </c>
-      <c r="C11" s="48" t="s">
+      <c r="B12" s="48" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="48"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
-      <c r="S11" s="37"/>
-      <c r="T11" s="37"/>
-      <c r="U11" s="37"/>
-    </row>
-    <row r="12" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>225</v>
-      </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31" t="s">
-        <v>201</v>
-      </c>
-      <c r="J12" s="31"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="34"/>
-    </row>
-    <row r="13" spans="1:21" s="28" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="37"/>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="37"/>
+      <c r="R12" s="37"/>
+      <c r="S12" s="37"/>
+      <c r="T12" s="37"/>
+      <c r="U12" s="37"/>
+    </row>
+    <row r="13" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="30" t="s">
         <v>183</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C13" s="31"/>
       <c r="D13" s="31"/>
@@ -1907,7 +1970,7 @@
       <c r="G13" s="32"/>
       <c r="H13" s="31"/>
       <c r="I13" s="31" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="J13" s="31"/>
       <c r="K13" s="31"/>
@@ -1924,52 +1987,50 @@
       <c r="T13" s="34"/>
       <c r="U13" s="34"/>
     </row>
-    <row r="14" spans="1:21" s="15" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="38"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="45"/>
-      <c r="N14" s="45"/>
-      <c r="O14" s="45"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="45"/>
-      <c r="R14" s="45"/>
-      <c r="S14" s="45"/>
-      <c r="T14" s="45"/>
-      <c r="U14" s="45"/>
-    </row>
-    <row r="15" spans="1:21" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="D15" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
+    <row r="14" spans="1:21" s="28" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="34"/>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
+      <c r="S14" s="34"/>
+      <c r="T14" s="34"/>
+      <c r="U14" s="34"/>
+    </row>
+    <row r="15" spans="1:21" s="15" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="38"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
       <c r="G15" s="44"/>
       <c r="H15" s="42"/>
       <c r="I15" s="42"/>
-      <c r="J15" s="42" t="s">
-        <v>13</v>
-      </c>
+      <c r="J15" s="42"/>
       <c r="K15" s="42"/>
-      <c r="L15" s="45"/>
+      <c r="L15" s="42"/>
       <c r="M15" s="45"/>
       <c r="N15" s="45"/>
       <c r="O15" s="45"/>
@@ -1980,141 +2041,117 @@
       <c r="T15" s="45"/>
       <c r="U15" s="45"/>
     </row>
-    <row r="16" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="63" t="s">
-        <v>230</v>
-      </c>
-      <c r="B16" s="63" t="s">
-        <v>231</v>
-      </c>
-      <c r="C16" s="64" t="s">
-        <v>244</v>
-      </c>
-      <c r="D16" s="64"/>
-      <c r="E16" s="64"/>
-      <c r="F16" s="64"/>
-      <c r="G16" s="64"/>
-      <c r="H16" s="65" t="s">
-        <v>164</v>
-      </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="64" t="s">
+    <row r="16" spans="1:21" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="K16" s="64"/>
-      <c r="L16" s="64"/>
-      <c r="M16" s="64"/>
-      <c r="N16" s="63"/>
-      <c r="O16" s="66"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="45"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="45"/>
+      <c r="O16" s="45"/>
+      <c r="P16" s="45"/>
+      <c r="Q16" s="45"/>
+      <c r="R16" s="45"/>
+      <c r="S16" s="45"/>
+      <c r="T16" s="45"/>
+      <c r="U16" s="45"/>
     </row>
     <row r="17" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="66" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="66" t="s">
+      <c r="A17" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="C17" s="66" t="s">
         <v>239</v>
-      </c>
-      <c r="C17" s="66" t="s">
-        <v>242</v>
       </c>
       <c r="D17" s="66"/>
       <c r="E17" s="66"/>
       <c r="F17" s="66"/>
       <c r="G17" s="66"/>
-      <c r="H17" s="63" t="s">
-        <v>238</v>
-      </c>
-      <c r="I17" s="64"/>
+      <c r="H17" s="65" t="s">
+        <v>164</v>
+      </c>
+      <c r="I17" s="66" t="s">
+        <v>240</v>
+      </c>
       <c r="J17" s="66" t="s">
         <v>13</v>
       </c>
       <c r="K17" s="66"/>
       <c r="L17" s="66"/>
       <c r="M17" s="66"/>
-      <c r="N17" s="66"/>
-      <c r="O17" s="66"/>
-      <c r="P17" s="34"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="34"/>
-      <c r="T17" s="34"/>
-    </row>
-    <row r="18" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="66" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="66" t="s">
-        <v>240</v>
-      </c>
-      <c r="C18" s="66" t="s">
-        <v>245</v>
-      </c>
+      <c r="N17" s="65" t="s">
+        <v>13</v>
+      </c>
+      <c r="O17" s="67"/>
+    </row>
+    <row r="18" spans="1:21" s="28" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="65" t="s">
+        <v>233</v>
+      </c>
+      <c r="C18" s="66"/>
       <c r="D18" s="66"/>
       <c r="E18" s="66"/>
-      <c r="F18" s="66" t="s">
-        <v>246</v>
-      </c>
-      <c r="G18" s="66" t="s">
-        <v>237</v>
-      </c>
-      <c r="H18" s="63" t="s">
-        <v>238</v>
-      </c>
-      <c r="I18" s="64"/>
-      <c r="J18" s="66" t="s">
-        <v>13</v>
-      </c>
+      <c r="F18" s="66"/>
+      <c r="G18" s="66"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="66" t="s">
+        <v>249</v>
+      </c>
+      <c r="J18" s="66"/>
       <c r="K18" s="66"/>
       <c r="L18" s="66"/>
       <c r="M18" s="66"/>
-      <c r="N18" s="66"/>
-      <c r="O18" s="66"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34"/>
-      <c r="S18" s="34"/>
-      <c r="T18" s="34"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="67"/>
     </row>
     <row r="19" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="66" t="s">
+      <c r="A19" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="B19" s="65" t="s">
         <v>241</v>
       </c>
-      <c r="B19" s="66" t="s">
-        <v>249</v>
-      </c>
-      <c r="C19" s="66" t="s">
-        <v>243</v>
-      </c>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66" t="s">
-        <v>237</v>
-      </c>
-      <c r="H19" s="63" t="s">
-        <v>247</v>
-      </c>
-      <c r="I19" s="64"/>
-      <c r="J19" s="66" t="s">
-        <v>13</v>
-      </c>
-      <c r="K19" s="66"/>
-      <c r="L19" s="66"/>
-      <c r="M19" s="66"/>
-      <c r="N19" s="66"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="34"/>
-    </row>
-    <row r="20" spans="1:21" s="15" customFormat="1" ht="63" x14ac:dyDescent="0.25">
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="65"/>
+    </row>
+    <row r="20" spans="1:21" s="15" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A20" s="38" t="s">
         <v>23</v>
       </c>
@@ -2127,16 +2164,16 @@
       <c r="D20" s="43"/>
       <c r="E20" s="42"/>
       <c r="F20" s="46" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H20" s="47" t="s">
         <v>164</v>
       </c>
       <c r="I20" s="47" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J20" s="42" t="s">
         <v>13</v>
@@ -2159,30 +2196,32 @@
         <v>202</v>
       </c>
     </row>
-    <row r="21" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="38"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="45"/>
-      <c r="O21" s="45"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="45"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="45"/>
-      <c r="U21" s="45"/>
-    </row>
-    <row r="22" spans="1:21" s="15" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" s="4" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="69" t="s">
+        <v>255</v>
+      </c>
+      <c r="B21" s="70" t="s">
+        <v>257</v>
+      </c>
+      <c r="C21" s="71" t="s">
+        <v>256</v>
+      </c>
+      <c r="D21" s="72"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="72"/>
+      <c r="H21" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="I21" s="73"/>
+      <c r="J21" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="K21" s="73"/>
+      <c r="L21" s="73"/>
+      <c r="M21" s="73"/>
+    </row>
+    <row r="22" spans="1:21" s="15" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A22" s="38" t="s">
         <v>24</v>
       </c>
@@ -2197,10 +2236,10 @@
       </c>
       <c r="E22" s="45"/>
       <c r="F22" s="46" t="s">
+        <v>258</v>
+      </c>
+      <c r="G22" s="43" t="s">
         <v>219</v>
-      </c>
-      <c r="G22" s="43" t="s">
-        <v>220</v>
       </c>
       <c r="H22" s="47" t="s">
         <v>164</v>
@@ -2413,7 +2452,7 @@
       <c r="T28" s="45"/>
       <c r="U28" s="45"/>
     </row>
-    <row r="29" spans="1:21" s="15" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
         <v>160</v>
       </c>
@@ -2651,28 +2690,28 @@
       <c r="T36" s="56"/>
       <c r="U36" s="56"/>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="52"/>
-      <c r="B37" s="57"/>
-      <c r="C37" s="58"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="56"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="45"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="56"/>
-      <c r="K37" s="56"/>
-      <c r="L37" s="56"/>
-      <c r="M37" s="56"/>
-      <c r="N37" s="56"/>
-      <c r="O37" s="56"/>
-      <c r="P37" s="56"/>
-      <c r="Q37" s="56"/>
-      <c r="R37" s="56"/>
-      <c r="S37" s="56"/>
-      <c r="T37" s="56"/>
-      <c r="U37" s="56"/>
+    <row r="37" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="B37" s="66" t="s">
+        <v>242</v>
+      </c>
+      <c r="C37" s="66"/>
+      <c r="D37" s="66"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="47"/>
+      <c r="I37" s="65" t="s">
+        <v>243</v>
+      </c>
+      <c r="J37" s="65"/>
+      <c r="K37" s="65"/>
+      <c r="L37" s="65"/>
+      <c r="M37" s="65"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="65"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="52" t="s">
@@ -2736,7 +2775,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5" customWidth="1"/>
@@ -3572,46 +3611,97 @@
         <v>170</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>168</v>
       </c>
       <c r="B81" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>168</v>
+      </c>
+      <c r="B82" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C81" s="25" t="s">
+      <c r="C82" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B82" s="25"/>
-      <c r="C82" s="25"/>
-    </row>
-    <row r="83" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="59" t="s">
-        <v>232</v>
-      </c>
-      <c r="B83" s="59" t="s">
-        <v>233</v>
-      </c>
-      <c r="C83" s="60" t="s">
-        <v>235</v>
-      </c>
-      <c r="D83" s="59"/>
-      <c r="E83" s="61"/>
-    </row>
-    <row r="84" spans="1:5" s="62" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B83" s="25"/>
+      <c r="C83" s="25"/>
+    </row>
+    <row r="84" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="59" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B84" s="59" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C84" s="60" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D84" s="59"/>
       <c r="E84" s="61"/>
+    </row>
+    <row r="85" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="59" t="s">
+        <v>228</v>
+      </c>
+      <c r="B85" s="59" t="s">
+        <v>230</v>
+      </c>
+      <c r="C85" s="60" t="s">
+        <v>232</v>
+      </c>
+      <c r="D85" s="59"/>
+      <c r="E85" s="61"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>246</v>
+      </c>
+      <c r="B87" s="62" t="s">
+        <v>247</v>
+      </c>
+      <c r="C87" t="s">
+        <v>248</v>
+      </c>
+      <c r="D87"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="B89" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="C89" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="D89" s="42"/>
+      <c r="E89" s="42"/>
+      <c r="F89" s="42"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="68" t="s">
+        <v>252</v>
+      </c>
+      <c r="B90" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="C90" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="D90" s="42"/>
+      <c r="E90" s="42"/>
+      <c r="F90" s="42"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3641,7 +3731,7 @@
     </row>
     <row r="2" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>250</v>

--- a/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_2_child.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_2_child.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\octobre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE4656A-D5FA-4029-ABAD-F6491644CB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FCCFF0-B269-4E8A-993B-6FEB83D9E085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2099,10 +2099,10 @@
       </c>
       <c r="K17" s="66"/>
       <c r="L17" s="66"/>
-      <c r="M17" s="66"/>
-      <c r="N17" s="65" t="s">
+      <c r="M17" s="65" t="s">
         <v>13</v>
       </c>
+      <c r="N17" s="65"/>
       <c r="O17" s="67"/>
     </row>
     <row r="18" spans="1:21" s="28" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">

--- a/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_2_child.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_2_child.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\octobre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FCCFF0-B269-4E8A-993B-6FEB83D9E085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DF9082-20E9-4C36-940B-207233EBDFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="264">
   <si>
     <t>type</t>
   </si>
@@ -711,9 +711,6 @@
     <t>L’âge doit être compris entre 5 et 14 ans pour l'enquête complémentaire, entre 10 et 14 ans pour l'enquête d'évaluation pratique</t>
   </si>
   <si>
-    <t>p_sppa2510</t>
-  </si>
-  <si>
     <t>C1</t>
   </si>
   <si>
@@ -780,9 +777,6 @@
     <t>p_index_cur</t>
   </si>
   <si>
-    <t>${p_index_init} + indexed-repeat(${position}, ${p_sppa2510}, count(${p_sppa2510}))</t>
-  </si>
-  <si>
     <t>concat(${p_code_id1})</t>
   </si>
   <si>
@@ -801,12 +795,6 @@
     <t>concat(${p_site_code}, '-', ${p_index_init} + position(..))</t>
   </si>
   <si>
-    <t>sn_sppa_impact_2510_2_child_v2</t>
-  </si>
-  <si>
-    <t>(2025 Oct) - 2. SCH/STH – Participant V2</t>
-  </si>
-  <si>
     <t>type_enquete_list</t>
   </si>
   <si>
@@ -816,29 +804,50 @@
     <t>PRATIQUE</t>
   </si>
   <si>
-    <t>select_one type_enquete_list</t>
-  </si>
-  <si>
     <t>Type d'enquete:</t>
   </si>
   <si>
     <t>p_type_enquete</t>
   </si>
   <si>
-    <t>if(${p_region}='COMPLEMENTAIRE', . &gt;= 5 and . &lt;= 14, . &gt;= 10 and . &lt;= 14)</t>
-  </si>
-  <si>
     <t>Ne fréquente pas</t>
   </si>
   <si>
     <t>Ne.fréquente.pas</t>
+  </si>
+  <si>
+    <t>sn_sppa_impact_2510_2_child_v3</t>
+  </si>
+  <si>
+    <t>(2025 Oct) - 2. SCH/STH – Participant V3</t>
+  </si>
+  <si>
+    <t>p_sppa2510_3</t>
+  </si>
+  <si>
+    <t>${p_index_init} + indexed-repeat(${position}, ${p_sppa2510_3}, count(${p_sppa2510_3}))</t>
+  </si>
+  <si>
+    <t>col_6</t>
+  </si>
+  <si>
+    <t>bind::db_add_col_7</t>
+  </si>
+  <si>
+    <t>if(${p_type_enquete}='COMPLEMENTAIRE', . &gt;= 5 and . &lt;= 14, . &gt;= 10 and . &lt;= 14)</t>
+  </si>
+  <si>
+    <t>not(selected(., 'Ne.fréquente.pas') and count-selected(.) &gt; 1)</t>
+  </si>
+  <si>
+    <t>Si "Ne fréquente pas" est sélectionné, aucune autre option ne doit l’être.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -922,6 +931,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -1520,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U39"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.625" style="27" customWidth="1"/>
@@ -1536,9 +1550,10 @@
     <col min="11" max="11" width="13.875" customWidth="1"/>
     <col min="12" max="12" width="16.625" customWidth="1"/>
     <col min="16" max="20" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="1" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
@@ -1602,8 +1617,11 @@
       <c r="U1" s="36" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="V1" s="36" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>14</v>
       </c>
@@ -1640,7 +1658,7 @@
       <c r="T2" s="42"/>
       <c r="U2" s="42"/>
     </row>
-    <row r="3" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
         <v>14</v>
       </c>
@@ -1671,7 +1689,7 @@
       <c r="T3" s="42"/>
       <c r="U3" s="42"/>
     </row>
-    <row r="4" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="38" t="s">
         <v>14</v>
       </c>
@@ -1706,29 +1724,28 @@
       <c r="T4" s="45"/>
       <c r="U4" s="45"/>
     </row>
-    <row r="5" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="43" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42" t="s">
+      <c r="B5" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>251</v>
+      </c>
+      <c r="D5" s="72"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="42"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
+      <c r="K5" s="73"/>
+      <c r="L5" s="73"/>
+      <c r="M5" s="73"/>
       <c r="O5" s="45" t="s">
         <v>194</v>
       </c>
@@ -1736,26 +1753,22 @@
       <c r="Q5" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="45"/>
-      <c r="U5" s="45"/>
-    </row>
-    <row r="6" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>173</v>
+        <v>110</v>
       </c>
       <c r="D6" s="44"/>
       <c r="E6" s="45"/>
       <c r="F6" s="45"/>
       <c r="G6" s="44"/>
-      <c r="H6" s="42"/>
+      <c r="H6" s="45"/>
       <c r="I6" s="42"/>
       <c r="J6" s="42" t="s">
         <v>13</v>
@@ -1768,23 +1781,23 @@
         <v>195</v>
       </c>
       <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="46" t="s">
-        <v>198</v>
-      </c>
+      <c r="Q6" s="46" t="s">
+        <v>197</v>
+      </c>
+      <c r="R6" s="45"/>
       <c r="S6" s="45"/>
       <c r="T6" s="45"/>
       <c r="U6" s="45"/>
     </row>
-    <row r="7" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="47" t="s">
-        <v>101</v>
+      <c r="B7" s="42" t="s">
+        <v>17</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D7" s="44"/>
       <c r="E7" s="45"/>
@@ -1796,7 +1809,7 @@
         <v>13</v>
       </c>
       <c r="K7" s="42"/>
-      <c r="L7" s="46"/>
+      <c r="L7" s="45"/>
       <c r="M7" s="45"/>
       <c r="N7" s="45"/>
       <c r="O7" s="45" t="s">
@@ -1804,195 +1817,199 @@
       </c>
       <c r="P7" s="45"/>
       <c r="Q7" s="45"/>
-      <c r="R7" s="45"/>
+      <c r="R7" s="46"/>
       <c r="S7" s="46" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="T7" s="45"/>
       <c r="U7" s="45"/>
     </row>
-    <row r="8" spans="1:21" s="15" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="38" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>181</v>
+        <v>101</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>174</v>
       </c>
       <c r="D8" s="44"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
       <c r="G8" s="44"/>
       <c r="H8" s="42"/>
       <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
+      <c r="J8" s="42" t="s">
+        <v>13</v>
+      </c>
       <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
+      <c r="L8" s="46"/>
       <c r="M8" s="45"/>
       <c r="N8" s="45"/>
-      <c r="O8" s="45"/>
+      <c r="O8" s="45" t="s">
+        <v>259</v>
+      </c>
       <c r="P8" s="45"/>
       <c r="Q8" s="45"/>
       <c r="R8" s="45"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="45"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46" t="s">
+        <v>199</v>
+      </c>
       <c r="U8" s="45"/>
     </row>
-    <row r="9" spans="1:21" s="28" customFormat="1" ht="126" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+    <row r="9" spans="1:22" s="15" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="D9" s="44"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="45"/>
+      <c r="R9" s="45"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="45"/>
+      <c r="U9" s="45"/>
+    </row>
+    <row r="10" spans="1:22" s="28" customFormat="1" ht="126" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="C10" s="44" t="s">
+        <v>243</v>
+      </c>
+      <c r="D10" s="44"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="63" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" s="63"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="63"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="64"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="34"/>
+      <c r="T10" s="34"/>
+      <c r="U10" s="34"/>
+    </row>
+    <row r="11" spans="1:22" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="65" t="s">
         <v>235</v>
       </c>
-      <c r="C9" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="D9" s="44"/>
-      <c r="E9" s="63"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="63"/>
-      <c r="J9" s="63" t="s">
-        <v>13</v>
-      </c>
-      <c r="K9" s="63"/>
-      <c r="L9" s="63"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="64"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="34"/>
-    </row>
-    <row r="10" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="65" t="s">
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
+      <c r="F11" s="65"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="J11" s="65"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="65"/>
+      <c r="M11" s="65"/>
+      <c r="N11" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="O11" s="65"/>
+    </row>
+    <row r="12" spans="1:22" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="B10" s="65" t="s">
-        <v>236</v>
-      </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="65" t="s">
-        <v>237</v>
-      </c>
-      <c r="J10" s="65"/>
-      <c r="K10" s="65"/>
-      <c r="L10" s="65"/>
-      <c r="M10" s="65"/>
-      <c r="N10" s="65" t="s">
-        <v>24</v>
-      </c>
-      <c r="O10" s="65"/>
-    </row>
-    <row r="11" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="B11" s="31" t="s">
+      <c r="B12" s="31" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33" t="s">
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="O11" s="34"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="34"/>
-    </row>
-    <row r="12" spans="1:21" s="29" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="37" t="s">
+      <c r="O12" s="34"/>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="34"/>
+      <c r="T12" s="34"/>
+      <c r="U12" s="34"/>
+    </row>
+    <row r="13" spans="1:22" s="29" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="B12" s="48" t="s">
-        <v>220</v>
-      </c>
-      <c r="C12" s="48" t="s">
+      <c r="B13" s="48" t="s">
+        <v>257</v>
+      </c>
+      <c r="C13" s="48" t="s">
         <v>185</v>
       </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="37"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="37"/>
-      <c r="U12" s="37"/>
-    </row>
-    <row r="13" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
-        <v>183</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31" t="s">
-        <v>201</v>
-      </c>
-      <c r="J13" s="31"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="34"/>
-    </row>
-    <row r="14" spans="1:21" s="28" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="37"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="37"/>
+      <c r="R13" s="37"/>
+      <c r="S13" s="37"/>
+      <c r="T13" s="37"/>
+      <c r="U13" s="37"/>
+    </row>
+    <row r="14" spans="1:22" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
         <v>183</v>
       </c>
       <c r="B14" s="31" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C14" s="31"/>
       <c r="D14" s="31"/>
@@ -2001,7 +2018,7 @@
       <c r="G14" s="32"/>
       <c r="H14" s="31"/>
       <c r="I14" s="31" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="J14" s="31"/>
       <c r="K14" s="31"/>
@@ -2018,52 +2035,50 @@
       <c r="T14" s="34"/>
       <c r="U14" s="34"/>
     </row>
-    <row r="15" spans="1:21" s="15" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="38"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="45"/>
-      <c r="O15" s="45"/>
-      <c r="P15" s="45"/>
-      <c r="Q15" s="45"/>
-      <c r="R15" s="45"/>
-      <c r="S15" s="45"/>
-      <c r="T15" s="45"/>
-      <c r="U15" s="45"/>
-    </row>
-    <row r="16" spans="1:21" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="D16" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
+    <row r="15" spans="1:22" s="28" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31" t="s">
+        <v>224</v>
+      </c>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="30"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
+      <c r="T15" s="34"/>
+      <c r="U15" s="34"/>
+    </row>
+    <row r="16" spans="1:22" s="15" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="38"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
       <c r="G16" s="44"/>
       <c r="H16" s="42"/>
       <c r="I16" s="42"/>
-      <c r="J16" s="42" t="s">
-        <v>13</v>
-      </c>
+      <c r="J16" s="42"/>
       <c r="K16" s="42"/>
-      <c r="L16" s="45"/>
+      <c r="L16" s="42"/>
       <c r="M16" s="45"/>
       <c r="N16" s="45"/>
       <c r="O16" s="45"/>
@@ -2074,154 +2089,163 @@
       <c r="T16" s="45"/>
       <c r="U16" s="45"/>
     </row>
-    <row r="17" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="65" t="s">
+    <row r="17" spans="1:22" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="42"/>
+      <c r="L17" s="45"/>
+      <c r="M17" s="45"/>
+      <c r="N17" s="45"/>
+      <c r="O17" s="45"/>
+      <c r="P17" s="45"/>
+      <c r="Q17" s="45"/>
+      <c r="R17" s="45"/>
+      <c r="S17" s="45"/>
+      <c r="T17" s="45"/>
+      <c r="U17" s="45"/>
+    </row>
+    <row r="18" spans="1:22" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="65" t="s">
+      <c r="B18" s="65" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" s="66" t="s">
         <v>238</v>
       </c>
-      <c r="C17" s="66" t="s">
-        <v>239</v>
-      </c>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="65" t="s">
-        <v>164</v>
-      </c>
-      <c r="I17" s="66" t="s">
-        <v>240</v>
-      </c>
-      <c r="J17" s="66" t="s">
-        <v>13</v>
-      </c>
-      <c r="K17" s="66"/>
-      <c r="L17" s="66"/>
-      <c r="M17" s="65" t="s">
-        <v>13</v>
-      </c>
-      <c r="N17" s="65"/>
-      <c r="O17" s="67"/>
-    </row>
-    <row r="18" spans="1:21" s="28" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="65" t="s">
-        <v>183</v>
-      </c>
-      <c r="B18" s="65" t="s">
-        <v>233</v>
-      </c>
-      <c r="C18" s="66"/>
       <c r="D18" s="66"/>
       <c r="E18" s="66"/>
       <c r="F18" s="66"/>
       <c r="G18" s="66"/>
-      <c r="H18" s="65"/>
+      <c r="H18" s="65" t="s">
+        <v>164</v>
+      </c>
       <c r="I18" s="66" t="s">
-        <v>249</v>
-      </c>
-      <c r="J18" s="66"/>
+        <v>239</v>
+      </c>
+      <c r="J18" s="66" t="s">
+        <v>13</v>
+      </c>
       <c r="K18" s="66"/>
       <c r="L18" s="66"/>
-      <c r="M18" s="66"/>
+      <c r="M18" s="65" t="s">
+        <v>13</v>
+      </c>
       <c r="N18" s="65"/>
       <c r="O18" s="67"/>
     </row>
-    <row r="19" spans="1:21" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" s="28" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A19" s="65" t="s">
         <v>183</v>
       </c>
       <c r="B19" s="65" t="s">
-        <v>241</v>
-      </c>
-      <c r="C19" s="65"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
+        <v>232</v>
+      </c>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
       <c r="H19" s="65"/>
-      <c r="I19" s="65" t="s">
+      <c r="I19" s="66" t="s">
+        <v>247</v>
+      </c>
+      <c r="J19" s="66"/>
+      <c r="K19" s="66"/>
+      <c r="L19" s="66"/>
+      <c r="M19" s="66"/>
+      <c r="N19" s="65"/>
+      <c r="O19" s="67"/>
+    </row>
+    <row r="20" spans="1:22" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" s="65" t="s">
+        <v>240</v>
+      </c>
+      <c r="C20" s="65"/>
+      <c r="D20" s="65"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="65"/>
+      <c r="H20" s="65"/>
+      <c r="I20" s="65" t="s">
         <v>201</v>
       </c>
-      <c r="J19" s="65"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="65"/>
-      <c r="M19" s="65"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="65"/>
-    </row>
-    <row r="20" spans="1:21" s="15" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A20" s="38" t="s">
+      <c r="J20" s="65"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="65"/>
+      <c r="M20" s="65"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="65"/>
+    </row>
+    <row r="21" spans="1:22" s="15" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="B21" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C21" s="43" t="s">
         <v>206</v>
       </c>
-      <c r="D20" s="43"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="46" t="s">
+      <c r="D21" s="43"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="G21" s="44" t="s">
         <v>226</v>
       </c>
-      <c r="G20" s="44" t="s">
-        <v>227</v>
-      </c>
-      <c r="H20" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="I20" s="47" t="s">
-        <v>244</v>
-      </c>
-      <c r="J20" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="N20" s="45"/>
-      <c r="O20" s="45"/>
-      <c r="P20" s="45"/>
-      <c r="Q20" s="45"/>
-      <c r="R20" s="45"/>
-      <c r="S20" s="45"/>
-      <c r="T20" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="U20" s="50" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" s="4" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="69" t="s">
-        <v>255</v>
-      </c>
-      <c r="B21" s="70" t="s">
-        <v>257</v>
-      </c>
-      <c r="C21" s="71" t="s">
-        <v>256</v>
-      </c>
-      <c r="D21" s="72"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="72"/>
       <c r="H21" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="I21" s="73"/>
-      <c r="J21" s="69" t="s">
+      <c r="I21" s="47" t="s">
+        <v>242</v>
+      </c>
+      <c r="J21" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="K21" s="73"/>
-      <c r="L21" s="73"/>
-      <c r="M21" s="73"/>
-    </row>
-    <row r="22" spans="1:21" s="15" customFormat="1" ht="63" x14ac:dyDescent="0.25">
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="N21" s="45"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="45"/>
+      <c r="R21" s="45"/>
+      <c r="S21" s="45"/>
+      <c r="T21" s="49"/>
+      <c r="U21" s="49" t="s">
+        <v>204</v>
+      </c>
+      <c r="V21" s="50" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" s="15" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A22" s="38" t="s">
         <v>24</v>
       </c>
@@ -2236,7 +2260,7 @@
       </c>
       <c r="E22" s="45"/>
       <c r="F22" s="46" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G22" s="43" t="s">
         <v>219</v>
@@ -2260,7 +2284,7 @@
       <c r="T22" s="45"/>
       <c r="U22" s="45"/>
     </row>
-    <row r="23" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
         <v>26</v>
       </c>
@@ -2293,7 +2317,7 @@
       <c r="T23" s="45"/>
       <c r="U23" s="45"/>
     </row>
-    <row r="24" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="38" t="s">
         <v>108</v>
       </c>
@@ -2326,7 +2350,7 @@
       <c r="T24" s="45"/>
       <c r="U24" s="45"/>
     </row>
-    <row r="25" spans="1:21" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
         <v>24</v>
       </c>
@@ -2363,7 +2387,7 @@
       <c r="T25" s="45"/>
       <c r="U25" s="45"/>
     </row>
-    <row r="26" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="38"/>
       <c r="B26" s="47"/>
       <c r="C26" s="43"/>
@@ -2386,7 +2410,7 @@
       <c r="T26" s="45"/>
       <c r="U26" s="45"/>
     </row>
-    <row r="27" spans="1:21" s="15" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" s="15" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38" t="s">
         <v>171</v>
       </c>
@@ -2398,8 +2422,12 @@
       </c>
       <c r="D27" s="44"/>
       <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="51"/>
+      <c r="F27" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="G27" s="51" t="s">
+        <v>263</v>
+      </c>
       <c r="H27" s="47" t="s">
         <v>164</v>
       </c>
@@ -2419,7 +2447,7 @@
       <c r="T27" s="45"/>
       <c r="U27" s="45"/>
     </row>
-    <row r="28" spans="1:21" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="38" t="s">
         <v>177</v>
       </c>
@@ -2452,7 +2480,7 @@
       <c r="T28" s="45"/>
       <c r="U28" s="45"/>
     </row>
-    <row r="29" spans="1:21" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A29" s="38" t="s">
         <v>160</v>
       </c>
@@ -2485,7 +2513,7 @@
       <c r="T29" s="45"/>
       <c r="U29" s="45"/>
     </row>
-    <row r="30" spans="1:21" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A30" s="38" t="s">
         <v>177</v>
       </c>
@@ -2518,7 +2546,7 @@
       <c r="T30" s="45"/>
       <c r="U30" s="45"/>
     </row>
-    <row r="31" spans="1:21" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" s="15" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A31" s="38" t="s">
         <v>177</v>
       </c>
@@ -2551,7 +2579,7 @@
       <c r="T31" s="45"/>
       <c r="U31" s="45"/>
     </row>
-    <row r="32" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A32" s="52" t="s">
         <v>18</v>
       </c>
@@ -2695,7 +2723,7 @@
         <v>183</v>
       </c>
       <c r="B37" s="66" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C37" s="66"/>
       <c r="D37" s="66"/>
@@ -2704,7 +2732,7 @@
       <c r="G37" s="65"/>
       <c r="H37" s="47"/>
       <c r="I37" s="65" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="J37" s="65"/>
       <c r="K37" s="65"/>
@@ -2768,6 +2796,7 @@
       <c r="U39" s="56"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -3616,10 +3645,10 @@
         <v>168</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C81" s="25" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3639,51 +3668,51 @@
     </row>
     <row r="84" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="59" t="s">
+        <v>227</v>
+      </c>
+      <c r="B84" s="59" t="s">
         <v>228</v>
       </c>
-      <c r="B84" s="59" t="s">
-        <v>229</v>
-      </c>
       <c r="C84" s="60" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D84" s="59"/>
       <c r="E84" s="61"/>
     </row>
     <row r="85" spans="1:6" s="62" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="59" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B85" s="59" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C85" s="60" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D85" s="59"/>
       <c r="E85" s="61"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>244</v>
+      </c>
+      <c r="B87" s="62" t="s">
+        <v>245</v>
+      </c>
+      <c r="C87" t="s">
         <v>246</v>
-      </c>
-      <c r="B87" s="62" t="s">
-        <v>247</v>
-      </c>
-      <c r="C87" t="s">
-        <v>248</v>
       </c>
       <c r="D87"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="68" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B89" s="42" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C89" s="42" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D89" s="42"/>
       <c r="E89" s="42"/>
@@ -3691,13 +3720,13 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="68" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B90" s="42" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C90" s="42" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="D90" s="42"/>
       <c r="E90" s="42"/>
@@ -3731,10 +3760,10 @@
     </row>
     <row r="2" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C2" t="s">
         <v>100</v>
